--- a/ig/hospitalnotification/StructureDefinition-medcom-hospitalNotification-messageHeader.xlsx
+++ b/ig/hospitalnotification/StructureDefinition-medcom-hospitalNotification-messageHeader.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$92</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3300" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="449">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T09:56:15+01:00</t>
+    <t>2026-02-10T12:55:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>MedCom (http://www.medcom.dk)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -262,6 +262,10 @@
     <t>The header for a message exchange that is either requesting or responding to an action.  The reference(s) that are the subject of the action as well as other information related to the action are typically transmitted in a bundle in which the MessageHeader resource instance is the first resource in the bundle.</t>
   </si>
   <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+  </si>
+  <si>
     <t>MSH / MSA / ERR</t>
   </si>
   <si>
@@ -515,40 +519,6 @@
   </si>
   <si>
     <t>Drives the behavior associated with this message.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>One of the message events defined as part of this version of FHIR.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/message-events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>MSH-9.2</t>
-  </si>
-  <si>
-    <t>./payload[classCode="CACT" and moodCode="EVN" and isNormalAct()]/code[isNormalDatatype()]/code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding</t>
-  </si>
-  <si>
-    <t>eventCoding</t>
-  </si>
-  <si>
-    <t>Code for the event this message represents or link to event definition</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -563,7 +533,13 @@
     <t>http://medcomfhir.dk/ig/terminology/ValueSet/medcom-messaging-messageTypes</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.id</t>
+    <t>MSH-9.2</t>
+  </si>
+  <si>
+    <t>./payload[classCode="CACT" and moodCode="EVN" and isNormalAct()]/code[isNormalDatatype()]/code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
   </si>
   <si>
     <t>MessageHeader.event[x].id</t>
@@ -585,9 +561,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.extension</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].extension</t>
   </si>
   <si>
@@ -603,9 +576,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.system</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].system</t>
   </si>
   <si>
@@ -630,9 +600,6 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.version</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].version</t>
   </si>
   <si>
@@ -654,9 +621,6 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.code</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].code</t>
   </si>
   <si>
@@ -678,9 +642,6 @@
     <t>./code</t>
   </si>
   <si>
-    <t>MessageHeader.event[x]:eventCoding.display</t>
-  </si>
-  <si>
     <t>MessageHeader.event[x].display</t>
   </si>
   <si>
@@ -700,9 +661,6 @@
   </si>
   <si>
     <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>MessageHeader.event[x]:eventCoding.userSelected</t>
   </si>
   <si>
     <t>MessageHeader.event[x].userSelected</t>
@@ -756,6 +714,9 @@
 </t>
   </si>
   <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>./communicationFunction[typeCode="RCV"]</t>
   </si>
   <si>
@@ -894,6 +855,9 @@
     <t>MessageHeader.destination:primary.id</t>
   </si>
   <si>
+    <t>MessageHeader.destination:primary.extension</t>
+  </si>
+  <si>
     <t>MessageHeader.destination:primary.extension:use</t>
   </si>
   <si>
@@ -940,15 +904,6 @@
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding</t>
-  </si>
-  <si>
-    <t>valueCoding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -957,19 +912,22 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.id</t>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:primary.extension:use.value[x].id</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].id</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.extension</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].extension</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].extension</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.system</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].system</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].system</t>
@@ -978,25 +936,25 @@
     <t>http://medcomfhir.dk/ig/terminology/CodeSystem/medcom-messaging-destinationUse</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.version</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].version</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].version</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.code</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].code</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].code</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.display</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].display</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].display</t>
   </si>
   <si>
-    <t>MessageHeader.destination:primary.extension:use.value[x]:valueCoding.userSelected</t>
+    <t>MessageHeader.destination:primary.extension:use.value[x].userSelected</t>
   </si>
   <si>
     <t>MessageHeader.destination.extension.value[x].userSelected</t>
@@ -1033,6 +991,9 @@
     <t>MessageHeader.destination:cc.id</t>
   </si>
   <si>
+    <t>MessageHeader.destination:cc.extension</t>
+  </si>
+  <si>
     <t>MessageHeader.destination:cc.extension:use</t>
   </si>
   <si>
@@ -1046,9 +1007,6 @@
   </si>
   <si>
     <t>MessageHeader.destination:cc.extension:use.value[x]</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -1057,25 +1015,25 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.id</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.extension</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.system</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.version</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.code</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.display</t>
-  </si>
-  <si>
-    <t>MessageHeader.destination:cc.extension:use.value[x]:valueCoding.userSelected</t>
+    <t>MessageHeader.destination:cc.extension:use.value[x].id</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].extension</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].system</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].version</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].code</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].display</t>
+  </si>
+  <si>
+    <t>MessageHeader.destination:cc.extension:use.value[x].userSelected</t>
   </si>
   <si>
     <t>MessageHeader.destination:cc.modifierExtension</t>
@@ -1298,6 +1256,9 @@
   </si>
   <si>
     <t>Need to be able to track why resources are being changed and report in the audit log/history of the resource.  May affect authorization.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Reason for event occurrence.</t>
@@ -1569,10 +1530,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -1762,20 +1723,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM93"/>
+  <dimension ref="A1:AM92"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="77.984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.1171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="26.453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.6875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="48.6953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="22.96875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="123.57421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.6953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1784,25 +1745,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="59.828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.98828125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="26.125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.8046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="28.94921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.90625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="23.56640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.28125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="160.15234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="140.38671875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2021,24 +1982,24 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2046,31 +2007,31 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2120,13 +2081,13 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>75</v>
@@ -2146,10 +2107,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2160,7 +2121,7 @@
         <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>75</v>
@@ -2169,16 +2130,16 @@
         <v>75</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2229,19 +2190,19 @@
         <v>75</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>75</v>
@@ -2255,10 +2216,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2269,28 +2230,28 @@
         <v>76</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2340,19 +2301,19 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
@@ -2366,10 +2327,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2380,7 +2341,7 @@
         <v>76</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>75</v>
@@ -2392,16 +2353,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2427,13 +2388,13 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2451,19 +2412,19 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>75</v>
@@ -2475,26 +2436,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>75</v>
@@ -2503,16 +2464,16 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2562,25 +2523,25 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>75</v>
@@ -2588,14 +2549,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2614,16 +2575,16 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2673,7 +2634,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2691,7 +2652,7 @@
         <v>75</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>75</v>
@@ -2699,10 +2660,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2725,13 +2686,13 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2770,17 +2731,17 @@
         <v>75</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2792,7 +2753,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -2804,15 +2765,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>75</v>
@@ -2822,25 +2783,25 @@
         <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2891,7 +2852,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2900,10 +2861,10 @@
         <v>77</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
@@ -2915,15 +2876,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>75</v>
@@ -2933,25 +2894,25 @@
         <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3002,7 +2963,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3011,10 +2972,10 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>75</v>
@@ -3028,14 +2989,14 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3048,25 +3009,25 @@
         <v>75</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>75</v>
@@ -3115,7 +3076,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3127,24 +3088,24 @@
         <v>75</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3152,34 +3113,34 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>75</v>
@@ -3189,7 +3150,7 @@
         <v>75</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>75</v>
@@ -3204,96 +3165,90 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC13" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF13" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AF13" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>167</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M14" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>75</v>
       </c>
@@ -3302,84 +3257,86 @@
         <v>75</v>
       </c>
       <c r="S14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="T14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X14" t="s" s="2">
+      <c r="AG14" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="Y14" s="2"/>
-      <c r="Z14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>166</v>
-      </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>75</v>
@@ -3391,15 +3348,17 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>75</v>
@@ -3436,37 +3395,37 @@
         <v>75</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>75</v>
@@ -3474,21 +3433,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>75</v>
@@ -3497,21 +3456,23 @@
         <v>75</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
       </c>
@@ -3547,37 +3508,37 @@
         <v>75</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>75</v>
@@ -3585,10 +3546,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3599,7 +3560,7 @@
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>75</v>
@@ -3608,23 +3569,21 @@
         <v>75</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>75</v>
       </c>
@@ -3672,25 +3631,25 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>75</v>
@@ -3698,10 +3657,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3709,10 +3668,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>75</v>
@@ -3721,21 +3680,21 @@
         <v>75</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
       </c>
@@ -3783,25 +3742,25 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>75</v>
@@ -3809,10 +3768,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3820,10 +3779,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>75</v>
@@ -3832,20 +3791,20 @@
         <v>75</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>75</v>
@@ -3894,25 +3853,25 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>75</v>
@@ -3920,10 +3879,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3934,7 +3893,7 @@
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>75</v>
@@ -3943,20 +3902,22 @@
         <v>75</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>75</v>
@@ -4005,25 +3966,25 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>75</v>
@@ -4031,10 +3992,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4042,10 +4003,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>75</v>
@@ -4054,22 +4015,22 @@
         <v>75</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>75</v>
@@ -4106,48 +4067,46 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4155,10 +4114,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>75</v>
@@ -4167,23 +4126,19 @@
         <v>75</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>232</v>
+        <v>169</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>75</v>
       </c>
@@ -4219,23 +4174,25 @@
         <v>75</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AC22" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>75</v>
@@ -4247,18 +4204,18 @@
         <v>75</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4266,10 +4223,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>75</v>
@@ -4281,13 +4238,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4326,62 +4283,62 @@
         <v>75</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
@@ -4390,13 +4347,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>129</v>
+        <v>230</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4435,17 +4392,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4454,10 +4413,10 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>75</v>
@@ -4471,44 +4430,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>243</v>
+        <v>130</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4556,7 +4517,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4565,16 +4526,16 @@
         <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>75</v>
@@ -4582,45 +4543,43 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -4669,25 +4628,25 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>75</v>
@@ -4695,10 +4654,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4709,7 +4668,7 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4718,20 +4677,20 @@
         <v>75</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
@@ -4780,25 +4739,25 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>75</v>
@@ -4806,10 +4765,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4817,10 +4776,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>75</v>
@@ -4829,20 +4788,22 @@
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O28" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4891,25 +4852,25 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>75</v>
@@ -4917,10 +4878,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4928,10 +4889,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4940,22 +4901,20 @@
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -5004,69 +4963,73 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AL29" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>218</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O30" t="s" s="2">
-        <v>275</v>
+        <v>221</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5115,74 +5078,68 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C31" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>232</v>
+        <v>169</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
@@ -5230,47 +5187,47 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -5282,15 +5239,17 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5327,64 +5286,62 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AC32" s="2"/>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
@@ -5393,13 +5350,13 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5450,7 +5407,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5459,10 +5416,10 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>75</v>
@@ -5476,10 +5433,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5490,7 +5447,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -5502,13 +5459,13 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5559,13 +5516,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -5577,7 +5534,7 @@
         <v>75</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>75</v>
@@ -5585,10 +5542,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5611,13 +5568,13 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5656,19 +5613,19 @@
         <v>75</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5680,7 +5637,7 @@
         <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>75</v>
@@ -5694,10 +5651,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5705,10 +5662,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -5720,16 +5677,16 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5737,7 +5694,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>75</v>
@@ -5779,13 +5736,13 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>75</v>
@@ -5797,7 +5754,7 @@
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>75</v>
@@ -5805,10 +5762,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5816,10 +5773,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -5831,13 +5788,13 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5849,7 +5806,7 @@
         <v>75</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>75</v>
+        <v>285</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>75</v>
@@ -5876,35 +5833,37 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
@@ -5912,23 +5871,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C38" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5940,13 +5897,13 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>295</v>
+        <v>169</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5958,7 +5915,7 @@
         <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>300</v>
+        <v>75</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>75</v>
@@ -5997,25 +5954,25 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>75</v>
@@ -6023,21 +5980,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
@@ -6049,15 +6006,17 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6094,37 +6053,37 @@
         <v>75</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>75</v>
@@ -6132,21 +6091,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -6155,21 +6114,23 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -6178,7 +6139,7 @@
         <v>75</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>75</v>
@@ -6205,37 +6166,37 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
@@ -6243,10 +6204,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6257,7 +6218,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -6266,23 +6227,21 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6291,7 +6250,7 @@
         <v>75</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>307</v>
+        <v>75</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>75</v>
@@ -6330,25 +6289,25 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -6356,10 +6315,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6370,7 +6329,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6379,21 +6338,21 @@
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
@@ -6441,25 +6400,25 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -6467,10 +6426,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6481,7 +6440,7 @@
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6490,20 +6449,20 @@
         <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6552,25 +6511,25 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6578,10 +6537,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6592,7 +6551,7 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>75</v>
@@ -6601,20 +6560,22 @@
         <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6663,25 +6624,25 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -6689,45 +6650,45 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6776,25 +6737,25 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
@@ -6802,45 +6763,43 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6889,25 +6848,25 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
@@ -6915,10 +6874,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6929,7 +6888,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
@@ -6938,20 +6897,20 @@
         <v>75</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -7000,36 +6959,36 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7037,32 +6996,34 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -7111,36 +7072,36 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL48" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AG48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="AM48" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7148,34 +7109,32 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>264</v>
+        <v>307</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>265</v>
+        <v>308</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -7224,69 +7183,73 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AG49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AL49" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>321</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>322</v>
+        <v>218</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>275</v>
+        <v>221</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -7335,40 +7298,38 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>277</v>
+        <v>224</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
@@ -7377,7 +7338,7 @@
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
@@ -7386,23 +7347,19 @@
         <v>75</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>232</v>
+        <v>169</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -7450,13 +7407,13 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>75</v>
@@ -7468,29 +7425,29 @@
         <v>75</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>237</v>
+        <v>172</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>238</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -7502,15 +7459,17 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7547,64 +7506,62 @@
         <v>75</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="AC52" s="2"/>
       <c r="AD52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -7613,13 +7570,13 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7670,7 +7627,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7679,10 +7636,10 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>75</v>
@@ -7696,10 +7653,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7710,7 +7667,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7722,13 +7679,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7779,13 +7736,13 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
@@ -7797,7 +7754,7 @@
         <v>75</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>75</v>
@@ -7805,10 +7762,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7831,13 +7788,13 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7876,19 +7833,19 @@
         <v>75</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7900,7 +7857,7 @@
         <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>75</v>
@@ -7914,10 +7871,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7925,10 +7882,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7940,16 +7897,16 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7957,7 +7914,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>75</v>
@@ -7999,13 +7956,13 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
@@ -8017,7 +7974,7 @@
         <v>75</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>75</v>
@@ -8025,10 +7982,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8036,10 +7993,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -8051,13 +8008,13 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8069,7 +8026,7 @@
         <v>75</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>75</v>
+        <v>318</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>75</v>
@@ -8096,35 +8053,37 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AC57" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>164</v>
+        <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>75</v>
@@ -8132,23 +8091,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>75</v>
@@ -8160,13 +8117,13 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>295</v>
+        <v>169</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>296</v>
+        <v>170</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8178,7 +8135,7 @@
         <v>75</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>332</v>
+        <v>75</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>75</v>
@@ -8217,25 +8174,25 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>75</v>
@@ -8243,21 +8200,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -8269,15 +8226,17 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8314,37 +8273,37 @@
         <v>75</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>75</v>
@@ -8352,21 +8311,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -8375,21 +8334,23 @@
         <v>75</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>75</v>
       </c>
@@ -8398,7 +8359,7 @@
         <v>75</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>75</v>
@@ -8425,37 +8386,37 @@
         <v>75</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>132</v>
+        <v>75</v>
       </c>
       <c r="AC60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>75</v>
@@ -8463,10 +8424,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8477,7 +8438,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>
@@ -8486,23 +8447,21 @@
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>98</v>
+        <v>168</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>192</v>
-      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
       </c>
@@ -8511,7 +8470,7 @@
         <v>75</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>307</v>
+        <v>75</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>75</v>
@@ -8550,25 +8509,25 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>75</v>
@@ -8576,10 +8535,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8590,7 +8549,7 @@
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -8599,21 +8558,21 @@
         <v>75</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>176</v>
+        <v>105</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>75</v>
       </c>
@@ -8661,25 +8620,25 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>75</v>
@@ -8687,10 +8646,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8701,7 +8660,7 @@
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
@@ -8710,20 +8669,20 @@
         <v>75</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>75</v>
@@ -8772,25 +8731,25 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>75</v>
@@ -8798,10 +8757,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8812,7 +8771,7 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>75</v>
@@ -8821,20 +8780,22 @@
         <v>75</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -8883,25 +8844,25 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -8909,45 +8870,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>75</v>
+        <v>234</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>222</v>
+        <v>130</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>226</v>
+        <v>153</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -8996,25 +8957,25 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>229</v>
+        <v>128</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>75</v>
@@ -9022,45 +8983,43 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>75</v>
@@ -9109,25 +9068,25 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>75</v>
+        <v>242</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>75</v>
@@ -9135,10 +9094,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9149,7 +9108,7 @@
         <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>75</v>
@@ -9158,20 +9117,20 @@
         <v>75</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>176</v>
+        <v>245</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -9220,36 +9179,36 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>255</v>
+        <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9257,32 +9216,34 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9331,36 +9292,36 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL68" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AG68" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="AM68" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9368,34 +9329,32 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>264</v>
+        <v>307</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>265</v>
+        <v>331</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9444,36 +9403,36 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK69" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>269</v>
-      </c>
       <c r="AL69" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9481,32 +9440,34 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9555,36 +9516,36 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>271</v>
+        <v>332</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>238</v>
+        <v>225</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9592,34 +9553,34 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
@@ -9668,36 +9629,36 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>276</v>
+        <v>342</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>277</v>
+        <v>343</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>238</v>
+        <v>344</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9708,7 +9669,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>75</v>
@@ -9717,22 +9678,22 @@
         <v>75</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -9781,36 +9742,36 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AG72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="B73" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9818,34 +9779,32 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L73" t="s" s="2">
-        <v>360</v>
-      </c>
       <c r="M73" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
@@ -9894,36 +9853,36 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>362</v>
+        <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9931,33 +9890,31 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>365</v>
+        <v>169</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>366</v>
+        <v>170</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>367</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -10005,47 +9962,47 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>364</v>
+        <v>171</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>368</v>
+        <v>172</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>369</v>
+        <v>75</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -10057,15 +10014,17 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
@@ -10114,25 +10073,25 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>75</v>
@@ -10140,14 +10099,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10160,24 +10119,26 @@
         <v>75</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>75</v>
       </c>
@@ -10225,7 +10186,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10237,13 +10198,13 @@
         <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>75</v>
@@ -10251,45 +10212,43 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>152</v>
+        <v>361</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>75</v>
@@ -10338,25 +10297,25 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>250</v>
+        <v>359</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>75</v>
+        <v>362</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>127</v>
+        <v>363</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>75</v>
@@ -10364,10 +10323,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10378,7 +10337,7 @@
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>75</v>
@@ -10387,20 +10346,20 @@
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>252</v>
+        <v>365</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>75</v>
@@ -10449,25 +10408,25 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>75</v>
@@ -10475,10 +10434,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10489,7 +10448,7 @@
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>75</v>
@@ -10498,20 +10457,20 @@
         <v>75</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>75</v>
@@ -10560,25 +10519,25 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>75</v>
@@ -10586,10 +10545,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10600,7 +10559,7 @@
         <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>75</v>
@@ -10609,20 +10568,20 @@
         <v>75</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>176</v>
+        <v>376</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>75</v>
@@ -10671,36 +10630,36 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10708,32 +10667,34 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>390</v>
+        <v>251</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>384</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="O81" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
@@ -10782,25 +10743,25 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>75</v>
@@ -10808,10 +10769,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10819,34 +10780,34 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>399</v>
+        <v>341</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>75</v>
@@ -10895,36 +10856,36 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>75</v>
+        <v>393</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10935,7 +10896,7 @@
         <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>75</v>
@@ -10944,22 +10905,20 @@
         <v>75</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>272</v>
+        <v>395</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>355</v>
+        <v>398</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>75</v>
@@ -10984,13 +10943,13 @@
         <v>75</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>75</v>
+        <v>399</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>75</v>
+        <v>401</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>75</v>
@@ -11008,36 +10967,36 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK83" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AG83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>405</v>
-      </c>
       <c r="AL83" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11048,7 +11007,7 @@
         <v>76</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -11057,21 +11016,19 @@
         <v>75</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>409</v>
+        <v>217</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" t="s" s="2">
-        <v>412</v>
-      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>75</v>
       </c>
@@ -11095,13 +11052,13 @@
         <v>75</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>413</v>
+        <v>75</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>414</v>
+        <v>75</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>75</v>
@@ -11119,36 +11076,36 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK84" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AG84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="AL84" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>417</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11159,7 +11116,7 @@
         <v>76</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>75</v>
@@ -11168,16 +11125,16 @@
         <v>75</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>419</v>
+        <v>169</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>420</v>
+        <v>170</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11228,25 +11185,25 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>418</v>
+        <v>171</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>421</v>
+        <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>422</v>
+        <v>172</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>75</v>
@@ -11254,21 +11211,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>75</v>
@@ -11280,15 +11237,17 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
@@ -11337,25 +11296,25 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>75</v>
@@ -11363,14 +11322,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>148</v>
+        <v>234</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11383,24 +11342,26 @@
         <v>75</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -11448,7 +11409,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -11460,13 +11421,13 @@
         <v>75</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>75</v>
@@ -11474,45 +11435,43 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>247</v>
+        <v>75</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>129</v>
+        <v>87</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>248</v>
+        <v>414</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>152</v>
+        <v>416</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -11561,25 +11520,25 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>75</v>
+        <v>417</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>127</v>
+        <v>418</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>75</v>
@@ -11587,10 +11546,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11598,10 +11557,10 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>75</v>
@@ -11610,20 +11569,22 @@
         <v>75</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -11648,13 +11609,13 @@
         <v>75</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>75</v>
+        <v>424</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>75</v>
@@ -11672,25 +11633,25 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK89" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AL89" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>75</v>
@@ -11698,10 +11659,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11709,10 +11670,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>75</v>
@@ -11721,22 +11682,22 @@
         <v>75</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>104</v>
+        <v>429</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O90" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>75</v>
@@ -11761,13 +11722,13 @@
         <v>75</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>437</v>
+        <v>75</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>438</v>
+        <v>75</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>75</v>
@@ -11785,36 +11746,36 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11822,34 +11783,34 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -11898,25 +11859,25 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>447</v>
+        <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>75</v>
@@ -11924,10 +11885,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11935,34 +11896,32 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>453</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>75</v>
@@ -12011,153 +11970,42 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="P93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AM93" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM93">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AM92">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI91">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
